--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0051.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0051.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Ride</t>
+          <t>Cưỡi</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Diligent Courier</t>
+          <t>Người Đưa Tin Cần Mẫn</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Falcon</t>
+          <t>Chim Ưng</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Cô Gái Vui Vẻ</t>
+          <t>Cô Gái Vui Tươi</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Gray Crested Gull</t>
+          <t>Mòng Biển Đỉnh Xám</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Orchestrate</t>
+          <t>Hòa Tấu</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Cyclone Swarm</t>
+          <t>Bầy Xoáy Lốc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Xem bức chân dung Maiden Được Ban Phước</t>
+          <t>Kiểm tra bức chân dung Thánh Nữ</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Lấy Bộ chuyển đổi Mô-đun</t>
+          <t>Lấy Bộ Chuyển Đổi Mô-đun đi</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Touch</t>
+          <t>Chạm</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Laser Neam</t>
+          <t>Tia Laser Neam</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Chạm vào ngọn lửa để di chuyển đến khu vực tiếp theo</t>
+          <t>Chạm vào ngọn lửa để tiến vào khu vực tiếp theo</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Bên trái</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Vào Second Coming of Solaris</t>
+          <t>Bước vào Sự Trở Lại Của Solaris.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Xiangping</t>
+          <t>Tường Bình</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Nobleman</t>
+          <t>Quý tộc</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Gắn Đá Neo</t>
+          <t>Chèn Đá Neo</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Scarefrost Deer</t>
+          <t>Hươu Băng Giá Kinh Hãi</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Scattered Royan Rune Fragments</t>
+          <t>Mảnh Rune Royan Rơi Rải</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Passionate Male</t>
+          <t>Chàng Trai Đầy Nhiệt Huyết</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Angry Father</t>
+          <t>Người Cha Giận Dữ</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>: Tethys Hệ thống</t>
+          <t>: Hệ Tethys</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Vào Nhà Thờ Mercury</t>
+          <t>Bước vào Nhà Thờ Mercury</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Súng giả</t>
+          <t>Súng đạo cụ</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Coffin the Fisherman</t>
+          <t>Coffin - Người Câu Cá</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Xueyi</t>
+          <t>Tuyết Nghi</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Tắt mô-đun năng lượng</t>
+          <t>Ngắt mô-đun năng lượng</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Bloodleaf Viburnum</t>
+          <t>Tử Đằng Tuyết</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Tuner - Actor 2</t>
+          <t>Điều Chỉnh Giả - Diễn Viên 2</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>: Blazing Guardian</t>
+          <t>: Người Bảo Vệ Lửa Thiêng</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Queuing Fan</t>
+          <t>Xếp hàng người hâm mộ</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Học sinh nóng tính</t>
+          <t>Học sinh Nóng Tính</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Khoan</t>
+          <t>Đợi đã</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Hình dáng cô gái trẻ</t>
+          <t>Bóng Dáng Cô Bé</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Anh ấy Chou</t>
+          <t>Hà Trù</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Kiểm tra bức tranh</t>
+          <t>Xem bức tranh</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Token</t>
+          <t>Mã Đổi</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Tôi muốn chuyển Tapes of Last Words</t>
+          <t>Tao muốn giao những Cuộn Băng Lời Trăn Trối</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Lianna</t>
+          <t>Liên Na</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Mutant Organism: Wild Boar</t>
+          <t>Sinh Vật Đột Biến: Lợn Rừng</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Chuỗi</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Vào Twilight Rise</t>
+          <t>Bước vào Twilight Rise</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Crybaby</t>
+          <t>Đồ mít ướt</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Thương nhân bí ẩn</t>
+          <t>Thương Nhân Bí Mật</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Goldcrest Scarab</t>
+          <t>Bọ Hung Mào Vàng</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Rời khỏi Nightmare Nest</t>
+          <t>Rời khỏi Tổ Chim Ác Mộng</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Despondent Gladiator</t>
+          <t>Đấu Sĩ Tuyệt Vọng</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Hãy đấu tay đôi</t>
+          <t>Ta đấu một trận đi.</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Gluttonous "Big Cat"</t>
+          <t>"Mèo Lớn" Háu Ăn</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Enter Somnoire</t>
+          <t>Vào Somnoire</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Tacet Field Ambience</t>
+          <t>Âm Thanh Nền Tổ Tacet</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Graduating Senior</t>
+          <t>Sinh Viên Năm Cuối</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Phantom: Chest Mimic</t>
+          <t>Bóng Ma: Hộp Giả Mạo</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Rương kho báu khổng lồ siêu cấp: Giá quá đắt</t>
+          <t>Rương Kho Báu Khổng Lồ: Giá Cả Quá Tay</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Fujian</t>
+          <t>Phúc Kiến</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Xinmei - Người hâm mộ sân khấu</t>
+          <t>Tân Mỹ - Người mê kịch nghệ</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Nhờ Cartethyia giúp đỡ</t>
+          <t>Nhờ Cartethyia trợ giúp</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>The False Sovereign</t>
+          <t>Kẻ Quân Vương Giả Mạo</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Uncle Fu</t>
+          <t>Chú Phú</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Enter "Tactical Simulacra II"</t>
+          <t>Vào "Tactical Simulacra II"</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>"Spear of Glory"</t>
+          <t>"Ngọn Giáo Vinh Quang"</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Shy Fan</t>
+          <t>Fan hâm mộ ngại ngùng</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Hoo</t>
+          <t>Hừm...</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Điểm hồi sinh đã kích hoạt</t>
+          <t>Đã kích hoạt Điểm Hồi Sinh</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Idealistic Novelist</t>
+          <t>Nhà Văn Lãng Mạn</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Kiểm tra thông báo thứ hai</t>
+          <t>Kiểm tra thông báo thứ hai đi</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Zhuqing</t>
+          <t>Chủ Khanh</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>The Eye</t>
+          <t>Con Mắt</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Bamboo Iris</t>
+          <t>Hoa Iris Tre</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Voidspawn: Nameless Explorer</t>
+          <t>Voidspawn: Nhà Thám Hiểm Vô Danh</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Obtain</t>
+          <t>Nhận Được</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Zhiqiu</t>
+          <t>Chí Thu</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Voidblight: Kronaclaw</t>
+          <t>Ô Nhiễm Hư Không: Móng Vuốt Krona</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Hoàn thành John Wicktorio: Không Debts for Old Men để mở khóa</t>
+          <t>Hoàn thành John Wicktorio: Không Nợ Cũ để mở khóa</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Tianlang</t>
+          <t>Thiên Lang</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Nightmare: Thundering Mephis - Eyes of Resentment</t>
+          <t>Ác Mộng: Thundering Mephis - Eyes of Resentment</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Professional Tuner</t>
+          <t>Người Điều Chỉnh Chuyên Nghiệp</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Lữ Khách Hỗ Trợ</t>
+          <t>Lữ Khách Đồng Hành</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Lấy Bộ chuyển đổi Mô-đun</t>
+          <t>Lấy Bộ Chuyển Đổi Mô-đun đi</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Chuyển bản nhạc</t>
+          <t>Giao bản nhạc này đi</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Creeping Torchpine Needle</t>
+          <t>Kim Tiêm Lửa Rón Rén</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Morph Painting</t>
+          <t>Bức Họa Hóa Hình</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Khách hàng hoảng loạn C</t>
+          <t>Khách hàng C hoảng hốt</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Curious Noble</t>
+          <t>Quý tộc tò mò</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Kỹ sư dày dạn kinh nghiệm</t>
+          <t>Kỹ Sư Lão Thành</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Grapple</t>
+          <t>Móc Câu</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Chop Chop: Leftless</t>
+          <t>Chop Chop: Không Tay Trái</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Septimont Patro Unit Platform</t>
+          <t>Bệ Đặt Đơn Vị Tuần Tra Septimont</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>- Eyes of Resentment</t>
+          <t>- Ánh Mắt Oán Hận</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Chain</t>
+          <t>Dây Xích</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Về bản thân</t>
+          <t>Về bản thân ta</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Path-driven Actor Test Generator</t>
+          <t>Trình Tạo Nhân Vật Theo Con Đường</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Simulation Training Device</t>
+          <t>Thiết Bị Huấn Luyện Mô Phỏng</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Initiate Lối chơi</t>
+          <t>Bắt đầu Trải nghiệm Gameplay</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>3_3 Motorbike Windfarm</t>
+          <t>Trang Trại Gió Xe Máy 3_3</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Thật sự</t>
+          <t>Thật</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Nhận Fulminate</t>
+          <t>Nhận được Fulminate</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Cửa ra vào Haven of Sprouts</t>
+          <t>Cửa Vào Mầm Xanh Thịnh Vượng</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Salvage</t>
+          <t>Thu hồi</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Voidspawn: Mining Reindeer</t>
+          <t>Voidspawn: Tuần Lộc Khai Thác</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Tar</t>
+          <t>Nhựa đường</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Mechascout</t>
+          <t>Tuần Thám Cơ Khí</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Xiaoyu</t>
+          <t>Tiểu Vũ</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Fortune Stick</t>
+          <t>Thẻ Xăm May Mắn</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Guest</t>
+          <t>Vị khách</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Đến khu ngầm Black Shores</t>
+          <t>Đến lòng đất Bãi Biển Đen</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Questless Knight</t>
+          <t>Hiệp Sĩ Không Nhiệm Vụ</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Dungeon_Air Wall Manager_Enter</t>
+          <t>Quản lý Rào Cản Không Gian_Vào</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Lianghui - Người mê kịch</t>
+          <t>Lương Hội - Người mê kịch trường</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Đi sạc năng lượng</t>
+          <t>Tiến lên và sạc năng lượng đi</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Move This Vase</t>
+          <t>Dời Chiếc Bình Này Đi</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Phoebe Cube</t>
+          <t>Khối Phoebe</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Xuống dưới</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Gourmet Rumors</t>
+          <t>Tin Đồn Ẩm Thực</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Dân Lưu Đày</t>
+          <t>Dân Lưu Đày Thường</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Cổng đá rời</t>
+          <t>Cổng Đá Lỏng Lẻo</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Knight of Sorrowful Aria</t>
+          <t>Hiệp Sĩ Khúc Bi Ca</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Vận hành thiết bị</t>
+          <t>Kích hoạt thiết bị</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>The Great Agon Schedule</t>
+          <t>Lịch Trình Đại Khổ Nạn</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>"Bliss"</t>
+          <t>"Hạnh phúc"</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Thành viên nhà Montelli bận rộn</t>
+          <t>Thành viên Gia tộc Montelli bận rộn</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Maxim</t>
+          <t>Tối đa</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Enter "Tactical Simulacra III"</t>
+          <t>Vào "Tactical Simulacra III"</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Mở cuốn *Overflowing Picture Book*</t>
+          <t>Mở Sách Tranh Tràn Đầy</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Học sinh run rẩy</t>
+          <t>Học Sinh Run Rẩy</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Quiz</t>
+          <t>Câu hỏi kiểm tra</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Grandino Head</t>
+          <t>Thủ lĩnh Grandino</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Explorer Phillips</t>
+          <t>Nhà thám hiểm Phillips</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>General Interaction</t>
+          <t>Tương tác với Đại tướng</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Caramel</t>
+          <t>Kẹo caramel</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Kiểm tra thứ Pero tìm thấy</t>
+          <t>Kiểm tra thứ Pero tìm được</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Wintry Bell</t>
+          <t>Chuông Mùa Đông</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Sabercat Reaver</t>
+          <t>Kẻ Tàn Sát Mèo Đao</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>KU-Repair</t>
+          <t>KU-Sửa chữa</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Điều tra hiện tượng bất thường</t>
+          <t>Kiểm tra điểm dị thường</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Record Player</t>
+          <t>Máy ghi âm</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Searchlight</t>
+          <t>Đèn Tìm Kiếm</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Thương nhân đi bán rong</t>
+          <t>Thương Nhân Lưu Động</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Averardo Bank</t>
+          <t>Ngân Hàng Averardo</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Noblewoman</t>
+          <t>Quý bà</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Feed</t>
+          <t>Cho ăn</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Libert</t>
+          <t>Tự Do</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Thành viên nhà Montelli</t>
+          <t>Thành Viên Gia Tộc Montelli</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Minghu</t>
+          <t>Minh Hổ</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Elder Wootter</t>
+          <t>Lão Wootter</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Tiến tới khu điều tra cuối cùng</t>
+          <t>Tiến đến khu vực điều tra cuối cùng</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Dosumu</t>
+          <t>Dosumu...</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Haunted Train</t>
+          <t>Con Tàu Ma Ám</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Electric Biến Đổier</t>
+          <t>Biến Áp Điện</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Play "A Small Miracle"</t>
+          <t>Phát "Điều Kỳ Diệu Nhỏ Bé"</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Guiding Acolyte</t>
+          <t>Hướng Dẫn Tu Sĩ</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Lahai-Roi Blocks: Infinite</t>
+          <t>Lahai-Roi Blocks: Vô tận</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Uncle Xie</t>
+          <t>Chú Tạ</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu mới</t>
+          <t>Nhà Nghiên Cứu Mới</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Bóng của Liel</t>
+          <t>Bóng dáng của Liel</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>New Arrival</t>
+          <t>Vị Khách Mới</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Lấy làn da Soliskin sáng bóng</t>
+          <t>Lấy Soliskin sáng lấp lánh</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Tiếp tục Neo Đậu trong Hỗn Loạn</t>
+          <t>Tiếp Tục Neo Giữ Trong Hỗn Loạn</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Contaminated Capsule Machine</t>
+          <t>Máy Capsule Bị Nhiễm Khuẩn</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Wanqin</t>
+          <t>Vạn Cần</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Yellowed Page</t>
+          <t>Trang Giấy Phai Màu</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Flamethrower</t>
+          <t>Phun Lửa</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Aero Predator</t>
+          <t>Thú Dữ Gió</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Xoay cần cẩu</t>
+          <t>Xoay cần bẩy</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Shorekeeper's Butterfly</t>
+          <t>Bươm Bướm Shorekeeper</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>: "Magic Fairy"</t>
+          <t>: "Tiên Nữ Phép Thuật"</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Music Sheet</t>
+          <t>Bản Nhạc</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Queen of the Night</t>
+          <t>: Nữ Hoàng Bóng Đêm</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Shiwu</t>
+          <t>Thạch Vũ</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Stellar Orbit Beats</t>
+          <t>Nhịp Quỹ Đạo Tinh Tú</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Snowwhite</t>
+          <t>Bạch Tuyết</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Chuyển thiết kế sàn thành "Khúc dạo đầu"</t>
+          <t>Đổi thiết kế sàn thành "Khúc Tĩnh Tâm"</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Triệu hồi Namipon Nhỏ</t>
+          <t>Triệu hồi Những Bé Namipon</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>: Lamenting Shadow</t>
+          <t>: Bóng Tối Than Thở</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Windchimer</t>
+          <t>Thú Gió</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Yoren</t>
+          <t>Yo-ren</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Obtain</t>
+          <t>Nhận Được</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Mảnh kính màu</t>
+          <t>Mảnh Kính Màu</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Giờ tôi đã nhìn rõ</t>
+          <t>Giờ ta đã nhìn rõ rồi...</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Kelpie Clone</t>
+          <t>Bản sao Kelpie</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Suspicious Ice Cube</t>
+          <t>Viên Băng Đáng Ngờ</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Đi đến tầng giữa</t>
+          <t>Đến tầng giữa nào</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Giao bản nhạc số 2</t>
+          <t>Giao bản nhạc số 2 đi</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Bảo cô gái đến thiết bị bên phải</t>
+          <t>Bảo cô bé đi đến thiết bị bên phải</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Ehlich</t>
+          <t>Ê lích</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Culinary Station</t>
+          <t>Trạm Ẩm Thực</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Ngồi xuống</t>
+          <t>Ngồi xuống đi</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Magnetic Base</t>
+          <t>Nền Từ Tính</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Oil Painting</t>
+          <t>Bức Tranh Dầu</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Yi Hong</t>
+          <t>Nhất Hồng</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Premium Trophy Chest</t>
+          <t>Rương Chiến Lợi Phẩm Cao Cấp</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Đặt Bộ chuyển đổi Mô-đun</t>
+          <t>Đặt Module Adapter</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Voidspawn: Sabercat Reaver</t>
+          <t>Voidspawn: Mãnh Hổ Cướp Phá</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Deceleration Ring</t>
+          <t>Nhẫn Giảm Tốc</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Nữ binh sĩ</t>
+          <t>Nữ Chiến Binh</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Hạ gục nhà nghiên cứu</t>
+          <t>Đặt nhà nghiên cứu xuống</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Nhân viên kỳ cựu</t>
+          <t>Nhân Viên Lão Luyện</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Painted Mantis Shrimp</t>
+          <t>Tôm Bọ Ngựa Sơn</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Kiểm tra thiết bị định vị</t>
+          <t>Kiểm tra bộ định vị</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Unusual Figures</t>
+          <t>Những Hình Dáng Kỳ Lạ</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Rogue: Inferno Rider</t>
+          <t>Kẻ Đi Lang Thang: Inferno Rider</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Weiqi Piece</t>
+          <t>Quân cờ Vây</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Cửa một chiều</t>
+          <t>Cửa Một Chiều</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Gaoshan</t>
+          <t>Cao Sơn</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Dungeon_Air Wall Manager_Round</t>
+          <t>Quản lý Rào Cản Không Gian_Vòng</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Fengbai</t>
+          <t>Phong Bạch</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Pet</t>
+          <t>Vuốt ve thú cưng</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Xiaoyu</t>
+          <t>Tiểu Vũ</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Hộp nhạc ballerina</t>
+          <t>Hộp nhạc vũ công ba-lê</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Thợ săn</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Worried Gladiator</t>
+          <t>Đấu Sĩ Lo Âu</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Ngọn Lửa Thiêng Huy hiệu Ba Anh Hùng</t>
+          <t>Lửa Thiêng Huyền Thoại Ba Anh Hùng</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Yanwu</t>
+          <t>Yến Vũ</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Chiếc thuyền gondola đã trở lại</t>
+          <t>Thuyền Gondola đã trở lại.</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Thiết bị xác thực chưa được kích hoạt</t>
+          <t>Thiết bị ủy quyền chưa được kích hoạt</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Warrant</t>
+          <t>Lệnh truy nã</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Xem quảng cáo</t>
+          <t>Xem quảng cáo đi</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Annunciator Cable</t>
+          <t>Dây cáp báo hiệu</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Đến vùng Lahai-Roi</t>
+          <t>Đến khu vực Lahai-Roi</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Tiến vào Thử Thách Tai Họa</t>
+          <t>Tiến vào Thử thách Tai ương</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Audio Log 3</t>
+          <t>Nhật Ký Âm Thanh 3</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Thử Thách Echo: Clang Bang</t>
+          <t>Thử Thách Tiếng Vọng: Clang Bang</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>About Jewel Boba</t>
+          <t>Về Trân Châu Trà Sữa</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Character Enhancement</t>
+          <t>Nâng cấp Nhân vật</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Geba</t>
+          <t>Cách Ba</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Đến Rừng Bjartr</t>
+          <t>Đến Bjartr Woods</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Quay về Journeying Paradise</t>
+          <t>Quay lại Thiên Đường Lang Thang</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Tacetite Fulminate: Group</t>
+          <t>Sấm Sét Tacetite: Nhóm</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Pedestal</t>
+          <t>Bệ Đỡ</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Fanatic Shark Grunt</t>
+          <t>Lính Cá Mập Cuồng Tín</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Spectro Drake</t>
+          <t>Drake Spectro</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Nhân viên Kho báu - Diễn viên 2</t>
+          <t>Nhân Viên Kho Tàng - Diễn Viên 2</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Điều tra tài liệu</t>
+          <t>Xem tài liệu</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Người đàn ông bị ám ảnh</t>
+          <t>Kẻ Cuồng Ám</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Enter City Hall</t>
+          <t>Vào Tòa Thị Chính</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Tạp chí mèo</t>
+          <t>Tạp chí Mèo</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Namipon Telephone Booth</t>
+          <t>Buồng điện thoại Namipon</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Primordia Bloom</t>
+          <t>Nở Nguyên Sơ</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Vào nửa sau</t>
+          <t>Bước vào Nửa Sau.</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Bộ Huấn Luyện Tự Động Toàn Năng: Loại Trạng Thái</t>
+          <t>Máy Huấn Luyện Chung: Loại Trạng Thái</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Mở khóa bức tượng</t>
+          <t>Mở bức tượng</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Mảnh thủy tinh vỡ</t>
+          <t>Mảnh Kính Vỡ</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Shadow of Resounding</t>
+          <t>: Bóng Tối Vang Dội</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>"King"</t>
+          <t>"Vua"</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Bức vẽ gia đình</t>
+          <t>Bức vẽ một gia đình</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Điểm hồi sinh</t>
+          <t>Điểm Hồi Sinh</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>The Great Beauty Yoyo</t>
+          <t>Nữ Thần Sắc Đẹp Yoyo</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Người đàn ông lo lắng</t>
+          <t>Người Đàn Ông Lo Lắng</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Perilla</t>
+          <t>Tía tô</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Người đàn ông Royan</t>
+          <t>Chàng trai Roya</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Rover Cube</t>
+          <t>Khối Lập Phương của Vận Mệnh Giả</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Ice Ursa</t>
+          <t>Gấu Bắc Cực Băng</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Septimont Patro Unit</t>
+          <t>Đơn Vị Tuần Tra Septimont</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Chenpi</t>
+          <t>Trần Bì</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Gloom Slough</t>
+          <t>Bãi Bùn U Ám</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Thành viên băng nhóm say xỉn</t>
+          <t>Tay Đàn Anh Say Xỉn</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Công dân Phân tích</t>
+          <t>Công Dân Phân Tích</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Chaotic Juncture: Ember</t>
+          <t>Điểm Giao Thoa Hỗn Loạn: Than Hồng</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Honest Official</t>
+          <t>Quan Viên Trung Thực</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Mya's Old Kiếm</t>
+          <t>Kiếm Cũ của Mya</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Stand</t>
+          <t>Đứng</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Uncle Ming</t>
+          <t>Chú Minh</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Thử nghiệm gameplay</t>
+          <t>Kiểm tra trò chơi</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Kronablight</t>
+          <t>Kẻ Ám Sương</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Jigsaw Puzzle</t>
+          <t>Trò Chơi Ghép Hình</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Suspension</t>
+          <t>Lơ Lửng</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Safe Position Detection</t>
+          <t>Phát Hiện Vị Trí An Toàn</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Nightmare: Lampylumen Myriad</t>
+          <t>Ác Mộng: Lampylumen Myriad</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Nền kính màu</t>
+          <t>Phần Đế Kính Màu</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Lingshan</t>
+          <t>Linh Sơn</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Singer</t>
+          <t>Ca sĩ</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Thử thách Echo: Cruisewing</t>
+          <t>Thử Thách Tiếng Vọng: Cruisewing</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Silver Lotus</t>
+          <t>Sen Bạc</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Hướng dẫn điều khiển đánh bại quái vật</t>
+          <t>Hướng dẫn điều khiển khi chiến đấu với quái vật</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Lianyue</t>
+          <t>Liên Nguyệt</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Hooscamp Clapperclaw</t>
+          <t>Quái Hooscamp Ném Đá</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Khách hàng thiếu kiên nhẫn</t>
+          <t>Khách Hàng Nóng Vội</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Nightmare: Hecate</t>
+          <t>Ác Mộng: Hecate</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Xem ghi chú do Ahab để lại</t>
+          <t>Xem lời nhắn Ahab để lại.</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Thử thách Echo: Cruisewing - vòng tròn di động</t>
+          <t>Thử Thách Tiếng Vọng: Cruisewing- mobile circle</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Xiangyi</t>
+          <t>Tường Nghị</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Terminal chưa kích hoạt</t>
+          <t>Thiết bị đầu cuối chưa kích hoạt</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Vào Sonoro Sphere</t>
+          <t>Bước vào Sonoro Sphere</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
